--- a/src/Pages/ImportExcelSympleFile/Family Form.xlsx
+++ b/src/Pages/ImportExcelSympleFile/Family Form.xlsx
@@ -1,33 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28227"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\MONIKA\ReactWebProj\Dhanani\src\Pages\ImportExcelSympleFile\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\react\Dhanani\src\Pages\ImportExcelSympleFile\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3BBD2E16-5FF6-4592-B7F7-74D26C07A51A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{A7C33EC3-129C-40FD-8885-DCD62834F011}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{8F04096A-5948-4255-BDCD-8EB826A0F342}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -36,77 +27,83 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
   <si>
-    <t>MemberID</t>
-  </si>
-  <si>
-    <t>FormNumber</t>
-  </si>
-  <si>
-    <t>BirthDate</t>
-  </si>
-  <si>
-    <t>SurName</t>
-  </si>
-  <si>
-    <t>MemberName</t>
-  </si>
-  <si>
-    <t>FatherName</t>
-  </si>
-  <si>
-    <t>GFatherName</t>
-  </si>
-  <si>
-    <t>RelationWithMainMember</t>
-  </si>
-  <si>
-    <t>Education</t>
-  </si>
-  <si>
-    <t>Mat_SurName</t>
-  </si>
-  <si>
-    <t>Mat_Name</t>
-  </si>
-  <si>
-    <t>Mat_FatherName</t>
-  </si>
-  <si>
-    <t>Mat_Village</t>
-  </si>
-  <si>
-    <t>Address</t>
-  </si>
-  <si>
-    <t>Business</t>
-  </si>
-  <si>
-    <t>Business_address</t>
-  </si>
-  <si>
-    <t>Foreign_Resident_Address</t>
-  </si>
-  <si>
-    <t>Mobile_1</t>
-  </si>
-  <si>
-    <t>Mobile_2</t>
-  </si>
-  <si>
-    <t>EmailID</t>
+    <t>સભ્ય નંબર</t>
+  </si>
+  <si>
+    <t>ફોર્મ નંબર</t>
+  </si>
+  <si>
+    <t>અટક</t>
+  </si>
+  <si>
+    <t>સભ્ય નુ નામ</t>
+  </si>
+  <si>
+    <t>સભ્ય ના  પિતા નુ નામ</t>
+  </si>
+  <si>
+    <t>સભ્ય ના દાદા</t>
+  </si>
+  <si>
+    <t xml:space="preserve">સભ્ય સાથે નું સગપણ </t>
+  </si>
+  <si>
+    <t>મોસાળ ની અટક</t>
+  </si>
+  <si>
+    <t>મામા નું નામ</t>
+  </si>
+  <si>
+    <t>મામા ના પિતા નુ નામ</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> મામા નું  ગામ</t>
+  </si>
+  <si>
+    <t>સરનામું</t>
+  </si>
+  <si>
+    <t>વ્યવસાય</t>
+  </si>
+  <si>
+    <t>વ્યવસાય નુ સરનામું</t>
+  </si>
+  <si>
+    <t>વિદેશ રહેઠાણ</t>
+  </si>
+  <si>
+    <t>મો.ન.(૧)</t>
+  </si>
+  <si>
+    <t>મો.ન.(૨)</t>
+  </si>
+  <si>
+    <t>ઈમેલ</t>
+  </si>
+  <si>
+    <t>અભ્યાસ</t>
+  </si>
+  <si>
+    <t>જન્મ તારીખ</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Consolas"/>
+      <family val="3"/>
     </font>
   </fonts>
   <fills count="2">
@@ -129,8 +126,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -445,77 +445,90 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{44A8A9BA-A994-4DC3-8FA4-3448CAD41637}">
-  <dimension ref="A1:U1"/>
+  <dimension ref="A1:T1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="8" max="8" width="26.85546875" customWidth="1"/>
-    <col min="12" max="12" width="16.42578125" customWidth="1"/>
-    <col min="13" max="13" width="20.28515625" customWidth="1"/>
-    <col min="17" max="17" width="11.85546875" customWidth="1"/>
-    <col min="18" max="18" width="15.5703125" customWidth="1"/>
-    <col min="20" max="20" width="11" customWidth="1"/>
+    <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.140625" customWidth="1"/>
+    <col min="5" max="5" width="19.42578125" customWidth="1"/>
+    <col min="6" max="6" width="25.5703125" customWidth="1"/>
+    <col min="7" max="7" width="14.140625" customWidth="1"/>
+    <col min="8" max="8" width="25.140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.7109375" customWidth="1"/>
+    <col min="10" max="10" width="17.85546875" customWidth="1"/>
+    <col min="11" max="11" width="16.85546875" customWidth="1"/>
+    <col min="12" max="12" width="35.42578125" customWidth="1"/>
+    <col min="13" max="13" width="20.42578125" customWidth="1"/>
+    <col min="14" max="14" width="9.42578125" customWidth="1"/>
+    <col min="15" max="15" width="15.28515625" customWidth="1"/>
+    <col min="16" max="16" width="24.5703125" customWidth="1"/>
+    <col min="17" max="17" width="30.28515625" customWidth="1"/>
+    <col min="18" max="18" width="13.140625" customWidth="1"/>
+    <col min="19" max="19" width="13.7109375" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+    <row r="1" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
         <v>1</v>
       </c>
       <c r="C1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="K1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="L1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" t="s">
+      <c r="M1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" t="s">
+      <c r="N1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" t="s">
+      <c r="O1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" t="s">
+      <c r="P1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" t="s">
+      <c r="Q1" t="s">
         <v>14</v>
       </c>
-      <c r="P1" t="s">
+      <c r="R1" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="S1" t="s">
         <v>16</v>
       </c>
-      <c r="S1" t="s">
+      <c r="T1" t="s">
         <v>17</v>
-      </c>
-      <c r="T1" t="s">
-        <v>18</v>
-      </c>
-      <c r="U1" t="s">
-        <v>19</v>
       </c>
     </row>
   </sheetData>
